--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-modalite-sortie.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-modalite-sortie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:40+00:00</t>
+    <t>2026-04-20T06:44:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3378,7 +3378,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>148</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>74</v>
@@ -3782,7 +3782,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>157</v>
       </c>
@@ -3797,13 +3797,13 @@
         <v>62</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>74</v>
@@ -3885,7 +3885,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>161</v>
       </c>
@@ -3900,13 +3900,13 @@
         <v>162</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>74</v>
@@ -4194,7 +4194,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>175</v>
       </c>
@@ -4209,13 +4209,13 @@
         <v>176</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>74</v>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-modalite-sortie.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-modalite-sortie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T06:44:24+00:00</t>
+    <t>2026-04-20T07:29:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-modalite-sortie.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-modalite-sortie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:29:37+00:00</t>
+    <t>2026-04-20T13:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4209,7 +4209,7 @@
         <v>176</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>75</v>
